--- a/conception/1_BDD/A_dictionnaire_donnees_qualicheck.xlsx
+++ b/conception/1_BDD/A_dictionnaire_donnees_qualicheck.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>VARCHAR(512)</t>
+          <t>VARCHAR(255)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>VARCHAR(512)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>VARCHAR(512)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>statique, playwright, manuel</t>
+          <t>statique, playwright, vision, manuel, ou une paire (ex. vision+statique)</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Extensible sans migration de schéma</t>
+          <t>Élargi VARCHAR(20)→(32) par la migration 0005 : l'ajout du composite a bien demandé une migration</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>vector(384)</t>
+          <t>vector(1536)</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1367,18 +1367,18 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Vecteur pgvector — All MiniLM L12 v2</t>
+          <t>Vecteur pgvector — text-embedding-3-small (Azure)</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>384 dimensions</t>
+          <t>1536 dimensions (native, non tronquée)</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr"/>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Index HNSW sur cette colonne</t>
+          <t>Index HNSW sur cette colonne. Élargie de vector(384) par la migration 0011</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>VARCHAR(256)</t>
+          <t>VARCHAR(512)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>Colonne vector(384) sur la table regle. All MiniLM L12 v2 via Infomaniak (gratuit). Index HNSW pour similarité cosinus. Dimension fixe sur toutes les phases — pas de migration prévue.</t>
+          <t>Colonne vector(1536) sur la table regle. text-embedding-3-small via Azure (phase de dev) : All MiniLM L12 v2 était visé mais sa fenêtre d'entrée de 128 tokens est incompatible avec « 1 règle = 1 chunk » (~319 tokens en moyenne). Index HNSW pour similarité cosinus. Élargie depuis vector(384) par la migration 0011 ; modèle souverain de production encore à évaluer, une nouvelle migration de dimension est possible.</t>
         </is>
       </c>
       <c r="C3" s="14" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Trois valeurs en V1 : statique, playwright, manuel. VARCHAR(20) intentionnel pour permettre l'ajout de nouvelles valeurs (ex : api, screenshot) sans migration de schéma.</t>
+          <t>Quatre valeurs simples : statique, playwright, vision, manuel — plus les composites en paire (ex. vision+statique) introduits par le prompt V4. VARCHAR(32) : la marge de VARCHAR(20) n'a pas suffi, la migration 0005 a dû l'élargir.</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
@@ -3028,7 +3028,7 @@
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>llm_provider</t>
+          <t>llm_model</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">

--- a/conception/1_BDD/A_dictionnaire_donnees_qualicheck.xlsx
+++ b/conception/1_BDD/A_dictionnaire_donnees_qualicheck.xlsx
@@ -924,7 +924,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>statique, playwright, vision, manuel, ou une paire (ex. vision+statique)</t>
+          <t>statique, playwright, vision, manuel, ou une paire composite. Deux operateurs : A+B (PUIS, ordre significatif) et A&amp;B (ET, verifications independantes)</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Quatre valeurs simples : statique, playwright, vision, manuel — plus les composites en paire (ex. vision+statique) introduits par le prompt V4. VARCHAR(32) : la marge de VARCHAR(20) n'a pas suffi, la migration 0005 a dû l'élargir.</t>
+          <t>Quatre valeurs simples : statique, playwright, vision, manuel — plus les paires composites introduites par le prompt V4, avec DEUX operateurs de sens distinct (prompt enrich_rule.md §1) : A+B signifie PUIS (B depend du resultat de A, donc l'ordre est la sequence d'execution et statique+playwright n'est pas playwright+statique), A&amp;B signifie ET (verifications independantes, sans ordre impose). Ne jamais normaliser l'ordre d'une paire + ni confondre les deux separateurs. VARCHAR(32) : la marge de VARCHAR(20) n'a pas suffi, la migration 0005 a dû l'élargir.</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
